--- a/research/traditional_assets/database/data/jamaica/jamaica_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.09575499999999999</v>
+        <v>0.206</v>
       </c>
       <c r="E2">
-        <v>-0.030245</v>
+        <v>0.0741</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,82 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>152.1</v>
+        <v>180.3</v>
       </c>
       <c r="L2">
-        <v>0.1415542112610516</v>
+        <v>0.1826562658291966</v>
       </c>
       <c r="M2">
-        <v>45.13</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.0169171945870975</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>0.2967126890203813</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>39.45</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.01478801964238858</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>0.2593688362919133</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>5.679999999999999</v>
-      </c>
-      <c r="T2">
-        <v>0.1258586306226457</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>2225.5</v>
+        <v>1461.8</v>
       </c>
       <c r="V2">
-        <v>0.8342392322974848</v>
+        <v>1.205011952848075</v>
       </c>
       <c r="W2">
-        <v>0.07970601107307965</v>
+        <v>0.1634336475707034</v>
       </c>
       <c r="X2">
-        <v>0.1043818664568029</v>
+        <v>0.2570648057212868</v>
       </c>
       <c r="Y2">
-        <v>-0.02467585538372322</v>
+        <v>-0.09363115815058334</v>
       </c>
       <c r="Z2">
-        <v>0.4081852830686112</v>
+        <v>0.3741140799696798</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.0781564599982239</v>
+        <v>0.1359487869260735</v>
       </c>
       <c r="AC2">
-        <v>-0.0781564599982239</v>
+        <v>-0.1359487869260735</v>
       </c>
       <c r="AD2">
-        <v>3085</v>
+        <v>3551.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3085</v>
+        <v>3551.3</v>
       </c>
       <c r="AG2">
-        <v>859.5</v>
+        <v>2089.5</v>
       </c>
       <c r="AH2">
-        <v>0.5362699254263216</v>
+        <v>0.7453824196121234</v>
       </c>
       <c r="AI2">
-        <v>0.5888191170576221</v>
+        <v>0.7310510930874058</v>
       </c>
       <c r="AJ2">
-        <v>0.2436777046949422</v>
+        <v>0.632683340398474</v>
       </c>
       <c r="AK2">
-        <v>0.2851881345809277</v>
+        <v>0.6152826855123675</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,7 +698,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Scotia Group Jamaica Limited (JMSE:SGJ)</t>
+          <t>NCB Financial Group Limited (JMSE:NCBFG)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,10 +707,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.00251</v>
+        <v>0.206</v>
       </c>
       <c r="E3">
-        <v>-0.0574</v>
+        <v>0.0741</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,212 +725,87 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>54.9</v>
+        <v>180.3</v>
       </c>
       <c r="L3">
-        <v>0.2222672064777328</v>
+        <v>0.1826562658291966</v>
       </c>
       <c r="M3">
-        <v>31.5</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.04259634888438134</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.5737704918032787</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>31.5</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.04259634888438134</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.5737704918032787</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>814.9</v>
+        <v>1461.8</v>
       </c>
       <c r="V3">
-        <v>1.101960784313725</v>
+        <v>1.205011952848075</v>
       </c>
       <c r="W3">
-        <v>0.07210401891252956</v>
+        <v>0.1634336475707034</v>
       </c>
       <c r="X3">
-        <v>0.07090198047114164</v>
+        <v>0.2570648057212868</v>
       </c>
       <c r="Y3">
-        <v>0.001202038441387915</v>
+        <v>-0.09363115815058334</v>
       </c>
       <c r="Z3">
-        <v>4.083792139940149</v>
+        <v>0.3741140799696798</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07090198047114164</v>
+        <v>0.1359487869260735</v>
       </c>
       <c r="AC3">
-        <v>-0.07090198047114164</v>
+        <v>-0.1359487869260735</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>3551.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>3551.3</v>
       </c>
       <c r="AG3">
-        <v>-814.9</v>
+        <v>2089.5</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.7453824196121234</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.7310510930874058</v>
       </c>
       <c r="AJ3">
-        <v>10.80769230769231</v>
+        <v>0.632683340398474</v>
       </c>
       <c r="AK3">
-        <v>11.20907840440166</v>
+        <v>0.6152826855123675</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Jamaica</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NCB Financial Group Limited (JMSE:NCBFG)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.189</v>
-      </c>
-      <c r="E4">
-        <v>-0.00309</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>97.2</v>
-      </c>
-      <c r="L4">
-        <v>0.1174622356495468</v>
-      </c>
-      <c r="M4">
-        <v>13.63</v>
-      </c>
-      <c r="N4">
-        <v>0.00706876879991702</v>
-      </c>
-      <c r="O4">
-        <v>0.1402263374485597</v>
-      </c>
-      <c r="P4">
-        <v>7.95</v>
-      </c>
-      <c r="Q4">
-        <v>0.004123016284617778</v>
-      </c>
-      <c r="R4">
-        <v>0.08179012345679013</v>
-      </c>
-      <c r="S4">
-        <v>5.679999999999999</v>
-      </c>
-      <c r="T4">
-        <v>0.4167278063096111</v>
-      </c>
-      <c r="U4">
-        <v>1410.6</v>
-      </c>
-      <c r="V4">
-        <v>0.7315631158593506</v>
-      </c>
-      <c r="W4">
-        <v>0.08730800323362975</v>
-      </c>
-      <c r="X4">
-        <v>0.1378617524424641</v>
-      </c>
-      <c r="Y4">
-        <v>-0.05055374920883435</v>
-      </c>
-      <c r="Z4">
-        <v>0.32174656868463</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.08541093952530615</v>
-      </c>
-      <c r="AC4">
-        <v>-0.08541093952530615</v>
-      </c>
-      <c r="AD4">
-        <v>3085</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>3085</v>
-      </c>
-      <c r="AG4">
-        <v>1674.4</v>
-      </c>
-      <c r="AH4">
-        <v>0.6153754089204501</v>
-      </c>
-      <c r="AI4">
-        <v>0.6859976429254407</v>
-      </c>
-      <c r="AJ4">
-        <v>0.4647754399600288</v>
-      </c>
-      <c r="AK4">
-        <v>0.5424914952211243</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/jamaica/jamaica_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.206</v>
+        <v>0.09980000000000001</v>
       </c>
       <c r="E2">
-        <v>0.0741</v>
+        <v>-0.08415</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,82 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>180.3</v>
+        <v>159.5</v>
       </c>
       <c r="L2">
-        <v>0.1826562658291966</v>
+        <v>0.130342404184032</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>33.8949</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.01881795469686875</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.212507210031348</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>33.8949</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.01881795469686875</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.212507210031348</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>1461.8</v>
+        <v>1918.9</v>
       </c>
       <c r="V2">
-        <v>1.205011952848075</v>
+        <v>1.065345325338663</v>
       </c>
       <c r="W2">
-        <v>0.1634336475707034</v>
+        <v>0.1015403728553787</v>
       </c>
       <c r="X2">
-        <v>0.2570648057212868</v>
+        <v>0.1434268257199024</v>
       </c>
       <c r="Y2">
-        <v>-0.09363115815058334</v>
+        <v>-0.04188645286452372</v>
       </c>
       <c r="Z2">
-        <v>0.3741140799696798</v>
+        <v>0.4128224954355738</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1359487869260735</v>
+        <v>0.0934788161919804</v>
       </c>
       <c r="AC2">
-        <v>-0.1359487869260735</v>
+        <v>-0.0934788161919804</v>
       </c>
       <c r="AD2">
-        <v>3551.3</v>
+        <v>3794.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3551.3</v>
+        <v>3794.1</v>
       </c>
       <c r="AG2">
-        <v>2089.5</v>
+        <v>1875.2</v>
       </c>
       <c r="AH2">
-        <v>0.7453824196121234</v>
+        <v>0.6780869658463353</v>
       </c>
       <c r="AI2">
-        <v>0.7310510930874058</v>
+        <v>0.6277672987193488</v>
       </c>
       <c r="AJ2">
-        <v>0.632683340398474</v>
+        <v>0.5100641932325101</v>
       </c>
       <c r="AK2">
-        <v>0.6152826855123675</v>
+        <v>0.4546049601202454</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -698,114 +701,239 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Scotia Group Jamaica Limited (JMSE:SGJ)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>0.0566</v>
+      </c>
+      <c r="E3">
+        <v>0.0617</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>110.7</v>
+      </c>
+      <c r="L3">
+        <v>0.324633431085044</v>
+      </c>
+      <c r="M3">
+        <v>27</v>
+      </c>
+      <c r="N3">
+        <v>0.03516998827667057</v>
+      </c>
+      <c r="O3">
+        <v>0.2439024390243902</v>
+      </c>
+      <c r="P3">
+        <v>27</v>
+      </c>
+      <c r="Q3">
+        <v>0.03516998827667057</v>
+      </c>
+      <c r="R3">
+        <v>0.2439024390243902</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>793.3</v>
+      </c>
+      <c r="V3">
+        <v>1.033346359254917</v>
+      </c>
+      <c r="W3">
+        <v>0.1524583390717532</v>
+      </c>
+      <c r="X3">
+        <v>0.0828224625095878</v>
+      </c>
+      <c r="Y3">
+        <v>0.06963587656216541</v>
+      </c>
+      <c r="Z3">
+        <v>8.714986710284194</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0.0828224625095878</v>
+      </c>
+      <c r="AC3">
+        <v>-0.0828224625095878</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>-793.3</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>30.98828125000011</v>
+      </c>
+      <c r="AK3">
+        <v>-40.06565656565643</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Jamaica</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>NCB Financial Group Limited (JMSE:NCBFG)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.206</v>
-      </c>
-      <c r="E3">
-        <v>0.0741</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>180.3</v>
-      </c>
-      <c r="L3">
-        <v>0.1826562658291966</v>
-      </c>
-      <c r="M3">
-        <v>-0</v>
-      </c>
-      <c r="N3">
-        <v>-0</v>
-      </c>
-      <c r="O3">
-        <v>-0</v>
-      </c>
-      <c r="P3">
-        <v>-0</v>
-      </c>
-      <c r="Q3">
-        <v>-0</v>
-      </c>
-      <c r="R3">
-        <v>-0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>1461.8</v>
-      </c>
-      <c r="V3">
-        <v>1.205011952848075</v>
-      </c>
-      <c r="W3">
-        <v>0.1634336475707034</v>
-      </c>
-      <c r="X3">
-        <v>0.2570648057212868</v>
-      </c>
-      <c r="Y3">
-        <v>-0.09363115815058334</v>
-      </c>
-      <c r="Z3">
-        <v>0.3741140799696798</v>
-      </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0.1359487869260735</v>
-      </c>
-      <c r="AC3">
-        <v>-0.1359487869260735</v>
-      </c>
-      <c r="AD3">
-        <v>3551.3</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>3551.3</v>
-      </c>
-      <c r="AG3">
-        <v>2089.5</v>
-      </c>
-      <c r="AH3">
-        <v>0.7453824196121234</v>
-      </c>
-      <c r="AI3">
-        <v>0.7310510930874058</v>
-      </c>
-      <c r="AJ3">
-        <v>0.632683340398474</v>
-      </c>
-      <c r="AK3">
-        <v>0.6152826855123675</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
+      <c r="D4">
+        <v>0.143</v>
+      </c>
+      <c r="E4">
+        <v>-0.23</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>48.8</v>
+      </c>
+      <c r="L4">
+        <v>0.0552849212643027</v>
+      </c>
+      <c r="M4">
+        <v>6.894900000000001</v>
+      </c>
+      <c r="N4">
+        <v>0.006671407837445574</v>
+      </c>
+      <c r="O4">
+        <v>0.1412889344262295</v>
+      </c>
+      <c r="P4">
+        <v>6.894900000000001</v>
+      </c>
+      <c r="Q4">
+        <v>0.006671407837445574</v>
+      </c>
+      <c r="R4">
+        <v>0.1412889344262295</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>1125.6</v>
+      </c>
+      <c r="V4">
+        <v>1.08911465892598</v>
+      </c>
+      <c r="W4">
+        <v>0.05062240663900414</v>
+      </c>
+      <c r="X4">
+        <v>0.204031188930217</v>
+      </c>
+      <c r="Y4">
+        <v>-0.1534087822912129</v>
+      </c>
+      <c r="Z4">
+        <v>0.3017674609415063</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.104135169874373</v>
+      </c>
+      <c r="AC4">
+        <v>-0.104135169874373</v>
+      </c>
+      <c r="AD4">
+        <v>3794.1</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>3794.1</v>
+      </c>
+      <c r="AG4">
+        <v>2668.5</v>
+      </c>
+      <c r="AH4">
+        <v>0.7859184688043748</v>
+      </c>
+      <c r="AI4">
+        <v>0.7253522473091556</v>
+      </c>
+      <c r="AJ4">
+        <v>0.7208265802269044</v>
+      </c>
+      <c r="AK4">
+        <v>0.6500450658936444</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/jamaica/jamaica_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.09980000000000001</v>
+        <v>0.0384</v>
       </c>
       <c r="E2">
-        <v>-0.08415</v>
+        <v>-0.149</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>159.5</v>
+        <v>84.7</v>
       </c>
       <c r="L2">
-        <v>0.130342404184032</v>
+        <v>0.1111402703057342</v>
       </c>
       <c r="M2">
-        <v>33.8949</v>
+        <v>31.3</v>
       </c>
       <c r="N2">
-        <v>0.01881795469686875</v>
+        <v>0.03947534367511666</v>
       </c>
       <c r="O2">
-        <v>0.212507210031348</v>
+        <v>0.3695395513577332</v>
       </c>
       <c r="P2">
-        <v>33.8949</v>
+        <v>31.3</v>
       </c>
       <c r="Q2">
-        <v>0.01881795469686875</v>
+        <v>0.03947534367511666</v>
       </c>
       <c r="R2">
-        <v>0.212507210031348</v>
+        <v>0.3695395513577332</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1918.9</v>
+        <v>1330.5</v>
       </c>
       <c r="V2">
-        <v>1.065345325338663</v>
+        <v>1.678017404464624</v>
       </c>
       <c r="W2">
-        <v>0.1015403728553787</v>
+        <v>0.09266958424507658</v>
       </c>
       <c r="X2">
-        <v>0.1434268257199024</v>
+        <v>0.2333315897350888</v>
       </c>
       <c r="Y2">
-        <v>-0.04188645286452372</v>
+        <v>-0.1406620054900122</v>
       </c>
       <c r="Z2">
-        <v>0.4128224954355738</v>
+        <v>0.2210202720338737</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.0934788161919804</v>
+        <v>0.1237256962016226</v>
       </c>
       <c r="AC2">
-        <v>-0.0934788161919804</v>
+        <v>-0.1237256962016226</v>
       </c>
       <c r="AD2">
-        <v>3794.1</v>
+        <v>3813.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3794.1</v>
+        <v>3813.6</v>
       </c>
       <c r="AG2">
-        <v>1875.2</v>
+        <v>2483.1</v>
       </c>
       <c r="AH2">
-        <v>0.6780869658463353</v>
+        <v>0.8278736567893195</v>
       </c>
       <c r="AI2">
-        <v>0.6277672987193488</v>
+        <v>0.7402461275670639</v>
       </c>
       <c r="AJ2">
-        <v>0.5100641932325101</v>
+        <v>0.7579670329670329</v>
       </c>
       <c r="AK2">
-        <v>0.4546049601202454</v>
+        <v>0.6498050401695757</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Scotia Group Jamaica Limited (JMSE:SGJ)</t>
+          <t>NCB Financial Group Limited (JMSE:NCBFG)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0566</v>
+        <v>0.0384</v>
       </c>
       <c r="E3">
-        <v>0.0617</v>
+        <v>-0.149</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,28 +728,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>110.7</v>
+        <v>84.7</v>
       </c>
       <c r="L3">
-        <v>0.324633431085044</v>
+        <v>0.1111402703057342</v>
       </c>
       <c r="M3">
-        <v>27</v>
+        <v>31.3</v>
       </c>
       <c r="N3">
-        <v>0.03516998827667057</v>
+        <v>0.03947534367511666</v>
       </c>
       <c r="O3">
-        <v>0.2439024390243902</v>
+        <v>0.3695395513577332</v>
       </c>
       <c r="P3">
-        <v>27</v>
+        <v>31.3</v>
       </c>
       <c r="Q3">
-        <v>0.03516998827667057</v>
+        <v>0.03947534367511666</v>
       </c>
       <c r="R3">
-        <v>0.2439024390243902</v>
+        <v>0.3695395513577332</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,182 +758,60 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>793.3</v>
+        <v>1330.5</v>
       </c>
       <c r="V3">
-        <v>1.033346359254917</v>
+        <v>1.678017404464624</v>
       </c>
       <c r="W3">
-        <v>0.1524583390717532</v>
+        <v>0.09266958424507658</v>
       </c>
       <c r="X3">
-        <v>0.0828224625095878</v>
+        <v>0.2333315897350888</v>
       </c>
       <c r="Y3">
-        <v>0.06963587656216541</v>
+        <v>-0.1406620054900122</v>
       </c>
       <c r="Z3">
-        <v>8.714986710284194</v>
+        <v>0.2210202720338737</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.0828224625095878</v>
+        <v>0.1237256962016226</v>
       </c>
       <c r="AC3">
-        <v>-0.0828224625095878</v>
+        <v>-0.1237256962016226</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>3813.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>3813.6</v>
       </c>
       <c r="AG3">
-        <v>-793.3</v>
+        <v>2483.1</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.8278736567893195</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.7402461275670639</v>
       </c>
       <c r="AJ3">
-        <v>30.98828125000011</v>
+        <v>0.7579670329670329</v>
       </c>
       <c r="AK3">
-        <v>-40.06565656565643</v>
+        <v>0.6498050401695757</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Jamaica</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NCB Financial Group Limited (JMSE:NCBFG)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.143</v>
-      </c>
-      <c r="E4">
-        <v>-0.23</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>48.8</v>
-      </c>
-      <c r="L4">
-        <v>0.0552849212643027</v>
-      </c>
-      <c r="M4">
-        <v>6.894900000000001</v>
-      </c>
-      <c r="N4">
-        <v>0.006671407837445574</v>
-      </c>
-      <c r="O4">
-        <v>0.1412889344262295</v>
-      </c>
-      <c r="P4">
-        <v>6.894900000000001</v>
-      </c>
-      <c r="Q4">
-        <v>0.006671407837445574</v>
-      </c>
-      <c r="R4">
-        <v>0.1412889344262295</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>1125.6</v>
-      </c>
-      <c r="V4">
-        <v>1.08911465892598</v>
-      </c>
-      <c r="W4">
-        <v>0.05062240663900414</v>
-      </c>
-      <c r="X4">
-        <v>0.204031188930217</v>
-      </c>
-      <c r="Y4">
-        <v>-0.1534087822912129</v>
-      </c>
-      <c r="Z4">
-        <v>0.3017674609415063</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.104135169874373</v>
-      </c>
-      <c r="AC4">
-        <v>-0.104135169874373</v>
-      </c>
-      <c r="AD4">
-        <v>3794.1</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>3794.1</v>
-      </c>
-      <c r="AG4">
-        <v>2668.5</v>
-      </c>
-      <c r="AH4">
-        <v>0.7859184688043748</v>
-      </c>
-      <c r="AI4">
-        <v>0.7253522473091556</v>
-      </c>
-      <c r="AJ4">
-        <v>0.7208265802269044</v>
-      </c>
-      <c r="AK4">
-        <v>0.6500450658936444</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/jamaica/jamaica_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0384</v>
+        <v>0.05309999999999999</v>
       </c>
       <c r="E2">
-        <v>-0.149</v>
+        <v>-0.03025</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>84.7</v>
+        <v>212.2</v>
       </c>
       <c r="L2">
-        <v>0.1111402703057342</v>
+        <v>0.1867628938567154</v>
       </c>
       <c r="M2">
-        <v>31.3</v>
+        <v>63.8</v>
       </c>
       <c r="N2">
-        <v>0.03947534367511666</v>
+        <v>0.03401215481394605</v>
       </c>
       <c r="O2">
-        <v>0.3695395513577332</v>
+        <v>0.3006597549481621</v>
       </c>
       <c r="P2">
-        <v>31.3</v>
+        <v>63.8</v>
       </c>
       <c r="Q2">
-        <v>0.03947534367511666</v>
+        <v>0.03401215481394605</v>
       </c>
       <c r="R2">
-        <v>0.3695395513577332</v>
+        <v>0.3006597549481621</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1330.5</v>
+        <v>1704.4</v>
       </c>
       <c r="V2">
-        <v>1.678017404464624</v>
+        <v>0.9086256530546967</v>
       </c>
       <c r="W2">
-        <v>0.09266958424507658</v>
+        <v>0.1247384325111744</v>
       </c>
       <c r="X2">
-        <v>0.2333315897350888</v>
+        <v>0.159918984046609</v>
       </c>
       <c r="Y2">
-        <v>-0.1406620054900122</v>
+        <v>-0.03518055153543459</v>
       </c>
       <c r="Z2">
-        <v>0.2210202720338737</v>
+        <v>0.3290980044124969</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1237256962016226</v>
+        <v>0.1051150435634315</v>
       </c>
       <c r="AC2">
-        <v>-0.1237256962016226</v>
+        <v>-0.1051150435634315</v>
       </c>
       <c r="AD2">
         <v>3813.6</v>
@@ -672,19 +672,19 @@
         <v>3813.6</v>
       </c>
       <c r="AG2">
-        <v>2483.1</v>
+        <v>2109.2</v>
       </c>
       <c r="AH2">
-        <v>0.8278736567893195</v>
+        <v>0.6702991528104897</v>
       </c>
       <c r="AI2">
-        <v>0.7402461275670639</v>
+        <v>0.6326476443264765</v>
       </c>
       <c r="AJ2">
-        <v>0.7579670329670329</v>
+        <v>0.5292848180677541</v>
       </c>
       <c r="AK2">
-        <v>0.6498050401695757</v>
+        <v>0.4878342122305485</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,117 +701,239 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Scotia Group Jamaica Limited (JMSE:SGJ)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>0.0678</v>
+      </c>
+      <c r="E3">
+        <v>0.0885</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>127.5</v>
+      </c>
+      <c r="L3">
+        <v>0.3408179631114675</v>
+      </c>
+      <c r="M3">
+        <v>32.5</v>
+      </c>
+      <c r="N3">
+        <v>0.03001200480192076</v>
+      </c>
+      <c r="O3">
+        <v>0.2549019607843137</v>
+      </c>
+      <c r="P3">
+        <v>32.5</v>
+      </c>
+      <c r="Q3">
+        <v>0.03001200480192076</v>
+      </c>
+      <c r="R3">
+        <v>0.2549019607843137</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>373.9</v>
+      </c>
+      <c r="V3">
+        <v>0.3452765721673284</v>
+      </c>
+      <c r="W3">
+        <v>0.1568072807772722</v>
+      </c>
+      <c r="X3">
+        <v>0.08650397771055161</v>
+      </c>
+      <c r="Y3">
+        <v>0.07030330306672054</v>
+      </c>
+      <c r="Z3">
+        <v>85.66521639569454</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0.08650397771055161</v>
+      </c>
+      <c r="AC3">
+        <v>-0.08650397771055161</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>-373.9</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.5273624823695344</v>
+      </c>
+      <c r="AK3">
+        <v>-0.7443758709934301</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Jamaica</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>NCB Financial Group Limited (JMSE:NCBFG)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="D4">
         <v>0.0384</v>
       </c>
-      <c r="E3">
+      <c r="E4">
         <v>-0.149</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
         <v>84.7</v>
       </c>
-      <c r="L3">
+      <c r="L4">
         <v>0.1111402703057342</v>
       </c>
-      <c r="M3">
+      <c r="M4">
         <v>31.3</v>
       </c>
-      <c r="N3">
+      <c r="N4">
         <v>0.03947534367511666</v>
       </c>
-      <c r="O3">
+      <c r="O4">
         <v>0.3695395513577332</v>
       </c>
-      <c r="P3">
+      <c r="P4">
         <v>31.3</v>
       </c>
-      <c r="Q3">
+      <c r="Q4">
         <v>0.03947534367511666</v>
       </c>
-      <c r="R3">
+      <c r="R4">
         <v>0.3695395513577332</v>
       </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
         <v>1330.5</v>
       </c>
-      <c r="V3">
+      <c r="V4">
         <v>1.678017404464624</v>
       </c>
-      <c r="W3">
+      <c r="W4">
         <v>0.09266958424507658</v>
       </c>
-      <c r="X3">
-        <v>0.2333315897350888</v>
-      </c>
-      <c r="Y3">
-        <v>-0.1406620054900122</v>
-      </c>
-      <c r="Z3">
+      <c r="X4">
+        <v>0.2333339903826663</v>
+      </c>
+      <c r="Y4">
+        <v>-0.1406644061375897</v>
+      </c>
+      <c r="Z4">
         <v>0.2210202720338737</v>
       </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0.1237256962016226</v>
-      </c>
-      <c r="AC3">
-        <v>-0.1237256962016226</v>
-      </c>
-      <c r="AD3">
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.1237261094163114</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1237261094163114</v>
+      </c>
+      <c r="AD4">
         <v>3813.6</v>
       </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
         <v>3813.6</v>
       </c>
-      <c r="AG3">
+      <c r="AG4">
         <v>2483.1</v>
       </c>
-      <c r="AH3">
+      <c r="AH4">
         <v>0.8278736567893195</v>
       </c>
-      <c r="AI3">
+      <c r="AI4">
         <v>0.7402461275670639</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ4">
         <v>0.7579670329670329</v>
       </c>
-      <c r="AK3">
+      <c r="AK4">
         <v>0.6498050401695757</v>
       </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
         <v>0</v>
       </c>
     </row>
